--- a/data/trans_orig/P33_2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana</t>
+          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana (tasa de respuesta: 97,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -576,12 +576,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,43</t>
+          <t>7,25; 7,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,4</t>
+          <t>7,26; 7,39</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,51</t>
+          <t>7,26; 7,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,32</t>
+          <t>7,1; 7,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 9,35</t>
+          <t>7,13; 9,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,3</t>
+          <t>7,01; 7,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,42</t>
+          <t>7,24; 7,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,19</t>
+          <t>6,47; 7,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 7,27</t>
+          <t>6,77; 7,28</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,43</t>
+          <t>7,19; 7,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,18</t>
+          <t>7,03; 7,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,24</t>
+          <t>7,11; 7,25</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 8,36</t>
+          <t>7,85; 8,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,2</t>
+          <t>7,36; 8,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,25</t>
+          <t>6,97; 7,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,72</t>
+          <t>7,24; 7,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Clase-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>7,35</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>7,33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>7,34</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,33</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,42</t>
+          <t>7,25; 7,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,43</t>
+          <t>7,25; 7,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,39</t>
+          <t>7,28; 7,4</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,41</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,23</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,31</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,48</t>
+          <t>7,29; 7,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,32</t>
+          <t>7,14; 7,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,39</t>
+          <t>7,25; 7,4</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>7,21</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>7,2</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,31</t>
+          <t>7,11; 7,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,31</t>
+          <t>7,01; 7,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 9,09</t>
+          <t>7,1; 7,29</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,33</t>
+          <t>7,35</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>7,16</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,27</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,42</t>
+          <t>7,27; 7,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 7,18</t>
+          <t>7,08; 7,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,28</t>
+          <t>7,2; 7,32</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,31</t>
+          <t>7,28</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,19</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,44</t>
+          <t>7,17; 7,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,18</t>
+          <t>7,05; 7,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,25</t>
+          <t>7,12; 7,25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>8,12</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,61</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,85; 8,36</t>
+          <t>7,87; 8,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,54</t>
+          <t>7,37; 7,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 7,72</t>
+          <t>7,51; 7,69</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,12</t>
+          <t>7,34; 7,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,26</t>
+          <t>7,21; 7,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,71</t>
+          <t>7,28; 7,34</t>
         </is>
       </c>
     </row>
